--- a/资料/未实装物品.xlsx
+++ b/资料/未实装物品.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27195" windowHeight="13140"/>
+    <workbookView windowWidth="14355" windowHeight="12990"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="94">
   <si>
     <t>有文件而无内容的物品</t>
   </si>
@@ -46,6 +46,9 @@
     <t>742_金塊</t>
   </si>
   <si>
+    <t>金块</t>
+  </si>
+  <si>
     <t>梅露露</t>
   </si>
   <si>
@@ -223,6 +226,9 @@
     <t>1732_エレメントガーブ</t>
   </si>
   <si>
+    <t>翠绿灵衣</t>
+  </si>
+  <si>
     <t>1733_セイントローブ（与1716重复）</t>
   </si>
   <si>
@@ -245,6 +251,21 @@
   </si>
   <si>
     <t>タンビーシュ</t>
+  </si>
+  <si>
+    <t>无用石</t>
+  </si>
+  <si>
+    <t>万能过滤剂</t>
+  </si>
+  <si>
+    <t>古老的壶</t>
+  </si>
+  <si>
+    <t>原初之土</t>
+  </si>
+  <si>
+    <t>轮回的齿轮</t>
   </si>
   <si>
     <t>素材的梨形宝石的文件名疑似错误，应为ペンデローク</t>
@@ -1259,33 +1280,36 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -1296,53 +1320,53 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
@@ -1350,15 +1374,15 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
@@ -1369,10 +1393,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
@@ -1383,13 +1407,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
@@ -1397,292 +1421,310 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/资料/未实装物品.xlsx
+++ b/资料/未实装物品.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14355" windowHeight="12990"/>
+    <workbookView windowWidth="27195" windowHeight="13140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="123">
   <si>
     <t>有文件而无内容的物品</t>
   </si>
@@ -43,6 +43,9 @@
     <t>/</t>
   </si>
   <si>
+    <t>据说是炼金术士的最终目标的石头。/只要用了这个，便可实现化学上不可能办到的调合。/形状会依据制作者而各不相同，它并没有存在一定的形状。</t>
+  </si>
+  <si>
     <t>742_金塊</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t>万能ろ過剤</t>
   </si>
   <si>
+    <t>为炼金术诞生之契机的物质，黄金的块状物。/虽然现在炼金术大多是用来制作黄金以外的东西啦。/即使是现在，要调合出黄金也很困难，/成品偶尔混有不纯物质的事似乎很常发生。</t>
+  </si>
+  <si>
     <t>10_使用アイテム</t>
   </si>
   <si>
@@ -73,6 +79,9 @@
     <t>治愈之铃</t>
   </si>
   <si>
+    <t>圣职人员御用，会发出祝福之音的钟。/当人越是感到困难时，它就越会授予伟大的祝福。/由于用力摇响它只会发出杂音，因此轻柔并有规律摇它非常重要。</t>
+  </si>
+  <si>
     <t>1324_時の石版</t>
   </si>
   <si>
@@ -88,6 +97,9 @@
     <t>亚兰德石晶</t>
   </si>
   <si>
+    <t>能操作时间流动的终极道具之一。/它还有项煞有其事的逸闻，/据说发明此配方的人，害怕其遭人用于作恶，/便故意提高制作难度，混入不必要的材料。</t>
+  </si>
+  <si>
     <t>1341_魔物の棲むツボ</t>
   </si>
   <si>
@@ -106,12 +118,18 @@
     <t>（万灵药）</t>
   </si>
   <si>
+    <t>封印着魔物的壶。/外表看似华丽，但在壶中会出现向外窥探的红色眼睛十分恐怖。/使用后就会从里面跑出猛兽，感觉就像弄蛇人从壶中叫出蛇。/虽然这个壶里装的东西比较凶暴啦。</t>
+  </si>
+  <si>
     <t>1342_精霊石</t>
   </si>
   <si>
     <t>托托莉</t>
   </si>
   <si>
+    <t>封印着精灵的石头。/只要遭受冲击，封印在里面的精灵就会跑出来大闹。/虽然感觉起来有点可怜，但既然都是精灵了，应该没关系吧……/或许。</t>
+  </si>
+  <si>
     <t>15_装備</t>
   </si>
   <si>
@@ -121,18 +139,27 @@
     <t>祈祷的符文</t>
   </si>
   <si>
+    <t>灌注魔法之力制作的古代护身具。/外表看起来老旧，正代表了其长时间受人使用。/会依据制作方法改变效果，因此若随身多带几个走，会更有安心感。</t>
+  </si>
+  <si>
     <t>1507_ブレイブマスク</t>
   </si>
   <si>
     <t>英勇面具</t>
   </si>
   <si>
+    <t>战士的面具。/而外观设计是源自某个边境地区中，作为勇气的象征而受到崇拜的精灵。/虽然外表看起来就很俗气，但考虑到其效果的强大，就令人不禁不烦恼。</t>
+  </si>
+  <si>
     <t>1513_まじない人形</t>
   </si>
   <si>
     <t>幸运魔法玩偶</t>
   </si>
   <si>
+    <t>松软的毛令人觉得很舒服的装饰品。/跟兔子的尾巴很像，/除了摸起来舒服以外，据说持有它还会受到幸运之神的眷顾哦。</t>
+  </si>
+  <si>
     <t>1712_銀糸の服</t>
   </si>
   <si>
@@ -142,12 +169,18 @@
     <t>聚酯羊毛</t>
   </si>
   <si>
+    <t>将银加工成纤维编织而成的衣服。/并不会因为使用了银而变得闪闪发亮的。/真要说的话，它给人很沉稳的色调，给人纯洁的印象。</t>
+  </si>
+  <si>
     <t>1713_輝く絹の服</t>
   </si>
   <si>
     <t>闪耀丝绢服</t>
   </si>
   <si>
+    <t>在庆祝典礼时穿戴，用丝绸编织的美丽礼服。/由于近卫兵等等平常就必须这么穿，因此内侧装有金属板，/在突然面临实战时也能应对。</t>
+  </si>
+  <si>
     <t>1714_竜織の服</t>
   </si>
   <si>
@@ -157,6 +190,9 @@
     <t>鳞片布料</t>
   </si>
   <si>
+    <t>用龙身体的一部分作为纤维编织而成的衣服。/以对刀刃或冲击、甚至是魔法攻击都有很强韧的防御力著称。/想取得材料就正如字面上所说得赌上性命，但它就是具有那样价值的珍品。</t>
+  </si>
+  <si>
     <t>1715_守護者の衣装</t>
   </si>
   <si>
@@ -166,6 +202,9 @@
     <t>天鹅绒布</t>
   </si>
   <si>
+    <t>在不久的以前，靠一己之力保护村落远离兽群袭击的男子所穿防具。/在亚兰德是很有名的故事，因而有很多的仿制品，/但很少有性能可以与之匹敌。</t>
+  </si>
+  <si>
     <t>1716_セイントローブ</t>
   </si>
   <si>
@@ -175,6 +214,9 @@
     <t>羽绒衬布</t>
   </si>
   <si>
+    <t>受到神明庇护的蓝色圣衣。/只有心灵纯洁的少女才能穿上。/有淡淡的圣光包覆着整件衣服，让邪恶之人连碰都碰不得。</t>
+  </si>
+  <si>
     <t>1722_ベルベットドレス</t>
   </si>
   <si>
@@ -184,6 +226,9 @@
     <t>光亮丝绸</t>
   </si>
   <si>
+    <t>在正式场合也能穿戴的礼服。/整体使用了柔软的布织成，能轻松吸收大部分冲击。/在宴会等场合突然遇到刺客袭击时，只要穿着它就能安心了。</t>
+  </si>
+  <si>
     <t>1723_貴婦人のドレス</t>
   </si>
   <si>
@@ -193,18 +238,27 @@
     <t>兽毛布料</t>
   </si>
   <si>
+    <t>洋溢高级感的贵妇礼服。/在备妥一级品的素材和一流工匠手艺的条件下才得以制成。/穿上去之后，身心都会端正起来，/连稚气的少女也会瞬间转变成倾世佳人。</t>
+  </si>
+  <si>
     <t>1724_煌びやかな薄衣</t>
   </si>
   <si>
     <t>灿烂的薄外衣</t>
   </si>
   <si>
+    <t>用比纸还薄的布制成的衣服。/由于穿着它也不会感觉到重量，因此在习惯前会让人觉得有点坐立难安。/可以让身体不管受到怎样的冲击，都能用像风一样轻盈的感觉避开。</t>
+  </si>
+  <si>
     <t>1725_薔薇の乙女</t>
   </si>
   <si>
     <t>蔷薇少女</t>
   </si>
   <si>
+    <t>备受瞩目的新进设计师所设计的作品。/从名字来看完全无法想象的毒性色彩，让人感受到独特的品味。/就别的层面来说，穿着它外出肯定会被男性盯着看准没错。</t>
+  </si>
+  <si>
     <t>1726_エーテルドレス</t>
   </si>
   <si>
@@ -214,6 +268,9 @@
     <t>医疗亚麻布</t>
   </si>
   <si>
+    <t>光看感觉就能被治愈，祖母绿的漂亮礼服。/被施予了治愈魔法。/虽然制作非常困难，但十分具有其价值。</t>
+  </si>
+  <si>
     <t>1731_氏族の祭儀服</t>
   </si>
   <si>
@@ -223,12 +280,18 @@
     <t>羽毛尼龙布</t>
   </si>
   <si>
+    <t>在开拓亚尔兹地区之前，住在这里的原住民所穿的衣服。/似乎会在祭祀之类的特殊场合穿。/给人一种就是有民族服装的感觉呢。</t>
+  </si>
+  <si>
     <t>1732_エレメントガーブ</t>
   </si>
   <si>
     <t>翠绿灵衣</t>
   </si>
   <si>
+    <t>流传是以前的人在森林拯救了有困难的妖精，妖精感谢人类而教导制法的衣服。/穿上它似乎就能受到精灵的庇护。</t>
+  </si>
+  <si>
     <t>1733_セイントローブ（与1716重复）</t>
   </si>
   <si>
@@ -241,6 +304,9 @@
     <t>ウィングキルト</t>
   </si>
   <si>
+    <t>像羽毛一样轻巧的布。/布里灌输了魔法之力。深红的布看起来很鲜艳。/有了这个，不管是制作怎样的装备，都不会令人感觉有异样吧。/虽然制作有点费工夫，但却有努力的价值在。</t>
+  </si>
+  <si>
     <t>怪鳥のつばさ</t>
   </si>
   <si>
@@ -250,25 +316,46 @@
     <t>原作中羽绒衬布的材料</t>
   </si>
   <si>
+    <t>巨大的鸟类魔物羽翼。/有的地区会在盛大的宴席上，调理成豪华的鸟翅料理来宴客。/不过一般是花时间把它加工成线，来做为武器或防具的材料。</t>
+  </si>
+  <si>
     <t>タンビーシュ</t>
   </si>
   <si>
+    <t>将强韧的野兽体毛，一根一根亲手织成的坚固布料。/虽然触感带有一些生硬，做成衣服略为不舒适，/但可制成除了打击外，也不畏炎气或寒气的衣服。</t>
+  </si>
+  <si>
     <t>无用石</t>
   </si>
   <si>
+    <t>乍看之下只觉得是普通的岩石。/但经由正确顺序精炼，便可萃取出万灵药的成分。/由于以前没有那样的技术，因此认为它毫无价值。</t>
+  </si>
+  <si>
     <t>万能过滤剂</t>
   </si>
   <si>
+    <t>固体的发泡滤材。/作为一种住宅用品而受到重重用。连脏水也能靠它就摇身一变成饮用水！/活用其强大净化力，也能用作药材的替代品。</t>
+  </si>
+  <si>
     <t>古老的壶</t>
   </si>
   <si>
+    <t>看上去就是很古老的壶。/不过不只是古老，也能感觉到包含了一段历史。有点神秘感。/不过我们王城的调理室好像也放有这个壶吧……还用来腌东西。</t>
+  </si>
+  <si>
     <t>原初之土</t>
   </si>
   <si>
+    <t>当这世界的大地首次诞生时，覆盖在表面上的土。/是万物的源头。/我们人类、动物跟植物，所有生命都是从这个土中创造出来的，/好像有部分的文献是这么写的吧。</t>
+  </si>
+  <si>
     <t>轮回的齿轮</t>
   </si>
   <si>
     <t>素材的梨形宝石的文件名疑似错误，应为ペンデローク</t>
+  </si>
+  <si>
+    <t>一旦开始运转就不会停下来，永远持续运作的永久机关试做品。/实际的构造看起来像是实现了永久机关这个理念，但这个机构看来无法转用于其他地方。</t>
   </si>
   <si>
     <t>缺失的中文翻译是还没在游戏中找到，后续会补充</t>
@@ -1234,8 +1321,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="16.25" customWidth="1"/>
@@ -1262,7 +1349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1275,41 +1362,47 @@
       <c r="D3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -1317,72 +1410,84 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
@@ -1390,13 +1495,16 @@
       <c r="D11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="H11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
@@ -1404,327 +1512,393 @@
       <c r="D12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="H12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="H13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>50</v>
+      </c>
+      <c r="H15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>57</v>
+      </c>
+      <c r="H16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>61</v>
+      </c>
+      <c r="H17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>65</v>
+      </c>
+      <c r="H18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>69</v>
+      </c>
+      <c r="H19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>73</v>
+      </c>
+      <c r="H20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="H21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>57</v>
+      </c>
+      <c r="H22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" t="s">
-        <v>52</v>
+      <c r="H25" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
+        <v>99</v>
+      </c>
+      <c r="H30" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+      <c r="H31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>103</v>
+      </c>
+      <c r="H32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>105</v>
+      </c>
+      <c r="H33" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>107</v>
+      </c>
+      <c r="H34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>109</v>
+      </c>
+      <c r="H35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>112</v>
+      </c>
+      <c r="H36" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
